--- a/data/trans_orig/IP2005-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2005-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65164</t>
+          <t>65283</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76298</t>
+          <t>76123</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60516</t>
+          <t>60137</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71769</t>
+          <t>71541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129874</t>
+          <t>129717</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145403</t>
+          <t>145009</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9646</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>21308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36443</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>331397</t>
+          <t>330679</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>352351</t>
+          <t>352059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>391292</t>
+          <t>392378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>412645</t>
+          <t>413568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>729422</t>
+          <t>730899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>759442</t>
+          <t>759286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>39170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59832</t>
+          <t>60550</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37425</t>
+          <t>36502</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58778</t>
+          <t>57692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81857</t>
+          <t>82013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111877</t>
+          <t>110400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145405</t>
+          <t>146192</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154759</t>
+          <t>155390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125808</t>
+          <t>126687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137620</t>
+          <t>138401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>275884</t>
+          <t>276219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>290345</t>
+          <t>290458</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>29741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>552531</t>
+          <t>550920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>576424</t>
+          <t>577113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>588504</t>
+          <t>589137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>614499</t>
+          <t>615367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1149037</t>
+          <t>1149480</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1184522</t>
+          <t>1184919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59614</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83507</t>
+          <t>85118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63040</t>
+          <t>62172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89035</t>
+          <t>88402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129054</t>
+          <t>128657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164539</t>
+          <t>164096</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72294</t>
+          <t>72510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82249</t>
+          <t>82084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63668</t>
+          <t>63207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74759</t>
+          <t>75049</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138888</t>
+          <t>139832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154660</t>
+          <t>154417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>19418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>31552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>362998</t>
+          <t>361134</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>383390</t>
+          <t>382760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>402303</t>
+          <t>403351</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>425067</t>
+          <t>424909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>771642</t>
+          <t>770852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>802508</t>
+          <t>801395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33840</t>
+          <t>34470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54232</t>
+          <t>56096</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>35395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>56953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75027</t>
+          <t>76140</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105893</t>
+          <t>106683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139886</t>
+          <t>140066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149470</t>
+          <t>149342</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144952</t>
+          <t>144528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153309</t>
+          <t>153320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288687</t>
+          <t>289082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301095</t>
+          <t>300988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21661</t>
+          <t>21266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>582311</t>
+          <t>582533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>608271</t>
+          <t>607939</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>621739</t>
+          <t>622122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>647056</t>
+          <t>646549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1211875</t>
+          <t>1211836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1248490</t>
+          <t>1248887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78003</t>
+          <t>77781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51896</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77213</t>
+          <t>76830</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110776</t>
+          <t>110379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147391</t>
+          <t>147430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47061</t>
+          <t>46938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53499</t>
+          <t>53787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50428</t>
+          <t>50075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60133</t>
+          <t>60077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100288</t>
+          <t>100417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112113</t>
+          <t>111974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>394384</t>
+          <t>396064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>413845</t>
+          <t>414450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>410147</t>
+          <t>410084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>430310</t>
+          <t>431129</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>812759</t>
+          <t>812302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>840355</t>
+          <t>840334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>24598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44664</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31429</t>
+          <t>30610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51592</t>
+          <t>51655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60432</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88028</t>
+          <t>88485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149375</t>
+          <t>148963</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158439</t>
+          <t>158386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>153243</t>
+          <t>153055</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163785</t>
+          <t>163582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,47 +4675,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>96,37%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>314271</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>306493</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>320207</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>96,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>314271</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>305923</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>319675</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>94,71%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>16683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,47 +4788,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>17570</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>11634</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>25348</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>3,51%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>17570</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>12166</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>25918</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>600248</t>
+          <t>600600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>621850</t>
+          <t>621485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>622476</t>
+          <t>623220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>648463</t>
+          <t>648223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1231855</t>
+          <t>1229970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1266165</t>
+          <t>1263683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>55776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49689</t>
+          <t>49929</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75676</t>
+          <t>74932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88362</t>
+          <t>90844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122672</t>
+          <t>124557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>43577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51681</t>
+          <t>51836</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41274</t>
+          <t>41270</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>53203</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88757</t>
+          <t>88207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102559</t>
+          <t>103230</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>391145</t>
+          <t>392405</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>416338</t>
+          <t>415980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>436786</t>
+          <t>434200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>461900</t>
+          <t>462246</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>835953</t>
+          <t>836015</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>872081</t>
+          <t>872279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>37882</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62717</t>
+          <t>61457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42976</t>
+          <t>42630</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68090</t>
+          <t>70676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86658</t>
+          <t>86460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122786</t>
+          <t>122724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114573</t>
+          <t>114511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129086</t>
+          <t>129072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149077</t>
+          <t>148861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165135</t>
+          <t>165478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269883</t>
+          <t>268412</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>291206</t>
+          <t>289760</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32965</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16944</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33002</t>
+          <t>33218</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>39857</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59734</t>
+          <t>61205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>559792</t>
+          <t>560137</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>590033</t>
+          <t>589932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>638014</t>
+          <t>638033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>673197</t>
+          <t>672062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1208371</t>
+          <t>1210300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1254796</t>
+          <t>1257116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65066</t>
+          <t>65167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95307</t>
+          <t>94962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73562</t>
+          <t>74697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108745</t>
+          <t>108726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147062</t>
+          <t>144742</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193487</t>
+          <t>191558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2005-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2005-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2007 (tasa de respuesta: 98,55%)</t>
+          <t>Menores según si sus dientes están sanos en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>66529</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>60442</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71380</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>81,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>74,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>71453</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>65283</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>76123</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>65183</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>75986</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>84,16%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>76,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>66529</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>60137</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>71541</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129717</t>
+          <t>129749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145009</t>
+          <t>144963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14886</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10035</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20973</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13449</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8779</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19619</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8916</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19719</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>15,84%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14886</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9874</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21278</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,28%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>21354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81415</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81415</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81415</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>84902</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>84902</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>84902</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>81415</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>81415</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>81415</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>402783</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>392532</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>412350</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>89,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>87,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>91,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>516</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>342239</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>330679</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>352059</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>332156</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>352736</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>87,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>84,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>402783</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>392378</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>413568</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>89,49%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>730899</t>
+          <t>731192</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>759286</t>
+          <t>759173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47287</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37720</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>57538</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>48990</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39170</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>60550</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>38493</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>59073</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>12,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>47287</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>36502</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>57692</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82013</t>
+          <t>82126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110400</t>
+          <t>110107</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>450070</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>450070</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>450070</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>590</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>391229</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>391229</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>391229</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>450070</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>450070</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>450070</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>133133</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>126335</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>137766</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>86,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>151349</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>146192</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>155390</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>145731</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>155166</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>94,65%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>91,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>133133</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>126687</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>138401</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>91,15%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>276219</t>
+          <t>275973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>290458</t>
+          <t>290890</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12921</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8288</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19719</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8557</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4516</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13714</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4740</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14175</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>5,35%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12921</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7653</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>19367</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>29987</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>146054</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>146054</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>146054</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>159906</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>159906</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>159906</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>146054</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>146054</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>146054</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>588309</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>614921</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>842</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>565042</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>550920</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>577113</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>552078</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>577011</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>88,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>86,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>602445</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>589137</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>615367</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>88,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1149480</t>
+          <t>1146804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1184919</t>
+          <t>1185783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>75094</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62618</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>89230</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>70996</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>58925</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>85118</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>59027</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>83960</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>11,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>75094</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>62172</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>88402</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128657</t>
+          <t>127793</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164096</t>
+          <t>166772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>677539</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>677539</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>677539</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>950</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>636038</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>636038</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>636038</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1019</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>677539</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>677539</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>677539</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2012 (tasa de respuesta: 99,54%)</t>
+          <t>Menores según si sus dientes están sanos en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69643</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63228</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>74321</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,29%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>89,95%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>77918</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>72510</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>82084</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>71963</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>82308</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>87,79%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>92,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>69643</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>63207</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>75049</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>84,29%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139832</t>
+          <t>139823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154417</t>
+          <t>154697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12982</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8304</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19397</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10841</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6675</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16249</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6451</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16796</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>12,21%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12982</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7576</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19418</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16967</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31552</t>
+          <t>31561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>415455</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>405334</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>425455</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>90,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>88,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>543</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>372951</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>361134</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>382760</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>361062</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>382348</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>89,39%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>415455</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>403351</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>424909</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>90,26%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>770852</t>
+          <t>773594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>801395</t>
+          <t>801937</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>44849</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34849</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>54970</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>44279</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>34470</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56096</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>34882</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>56168</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10,61%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>44849</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>35395</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>56953</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76140</t>
+          <t>75598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106683</t>
+          <t>103941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>460304</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>460304</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>460304</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>604</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>417230</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>417230</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>417230</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>460304</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>460304</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>460304</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>150234</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>145503</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>153298</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>93,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>145620</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>140066</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>149342</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>139969</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>149682</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>94,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>150234</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>144528</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>153320</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>96,29%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289082</t>
+          <t>288360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>300988</t>
+          <t>300780</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5788</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10519</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8705</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4983</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14259</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4643</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14356</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>5,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5788</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11494</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>21988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154325</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154325</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154325</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>635333</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>621686</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>646164</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>90,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>88,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>861</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>596489</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>582533</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>607939</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>583154</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>609046</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>90,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>88,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>635333</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>622122</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>646549</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1211836</t>
+          <t>1213248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1248887</t>
+          <t>1248464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -3473,67 +3473,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>63619</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52788</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>77266</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>63825</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>52375</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>77781</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>51268</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>77160</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>9,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>63619</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>52403</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>76830</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110379</t>
+          <t>110802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147430</t>
+          <t>146018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>698952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>698952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>698952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>660314</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>660314</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>660314</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>698952</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>698952</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>698952</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2016 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según si sus dientes están sanos en 2016 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55853</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50474</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60090</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>51267</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46938</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53787</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>47384</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53617</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>92,83%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>55853</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>50075</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60077</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>83,77%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100417</t>
+          <t>100294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111974</t>
+          <t>112037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10821</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16200</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3959</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1439</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8288</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7842</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>7,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10821</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6597</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>16599</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>21606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>66674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>66674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>66674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55226</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55226</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55226</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>66674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>66674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>66674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>421421</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>410599</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>431806</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>93,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>609</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>405736</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>396064</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>414450</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>395805</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>413928</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>92,41%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>90,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>421421</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>410084</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>431129</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>812302</t>
+          <t>813478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>840334</t>
+          <t>841153</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40318</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29933</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>51140</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>33312</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24598</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42984</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25120</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>43243</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>7,59%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>40318</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>30610</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>51655</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>59634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88485</t>
+          <t>87309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>461739</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>461739</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>461739</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>439048</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>439048</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>439048</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>461739</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>461739</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>461739</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>159336</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>152801</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>163525</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>90,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>154934</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>148963</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>158386</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>149600</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>158413</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>95,58%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>91,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>159336</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>153055</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>163582</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>93,87%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>306493</t>
+          <t>305786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>320207</t>
+          <t>320231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16937</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>7168</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3716</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13139</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12502</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>4,42%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10402</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>6156</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>16683</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25348</t>
+          <t>26055</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>162102</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>162102</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>162102</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>623795</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>648383</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>918</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>611937</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>600600</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>621485</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>599300</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>621013</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>93,23%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>636612</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>623220</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>648223</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1229970</t>
+          <t>1231256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1263683</t>
+          <t>1264212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61540</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>49769</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>74357</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>44439</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34891</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>55776</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>35363</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>57076</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>61540</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>49929</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>74932</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90844</t>
+          <t>90315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124557</t>
+          <t>123271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>698152</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>698152</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>698152</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>656376</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>656376</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>656376</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>698152</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>698152</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>698152</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si sus dientes están sanos en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43479</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37025</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48735</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>79,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>67,4%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>48572</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>43577</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51836</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>90,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>48222</t>
+          <t>40665</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41270</t>
+          <t>35960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53203</t>
+          <t>43608</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>96794</t>
+          <t>84144</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88207</t>
+          <t>77217</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103230</t>
+          <t>90220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11454</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6198</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17908</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5127</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1863</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10122</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>416210</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>402560</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>427801</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>89,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>86,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>91,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>557</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>404227</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>392405</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>415980</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>450449</t>
+          <t>376936</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>434200</t>
+          <t>364533</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>462246</t>
+          <t>387849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>854677</t>
+          <t>793146</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>836015</t>
+          <t>776401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>872279</t>
+          <t>809646</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50034</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38443</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>63684</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>49635</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37882</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>61457</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>54427</t>
+          <t>49536</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42630</t>
+          <t>38623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70676</t>
+          <t>61939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104062</t>
+          <t>99570</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86460</t>
+          <t>83070</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122724</t>
+          <t>116315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466244</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466244</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466244</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>629</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>453862</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>453862</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>453862</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>504876</t>
+          <t>426472</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>504876</t>
+          <t>426472</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>504876</t>
+          <t>426472</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>958739</t>
+          <t>892716</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>958739</t>
+          <t>892716</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>958739</t>
+          <t>892716</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>145766</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>136985</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>152921</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>87,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>81,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>122335</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>114511</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>129072</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>82,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>77,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>158419</t>
+          <t>123490</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148861</t>
+          <t>115367</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165478</t>
+          <t>130305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>280755</t>
+          <t>269256</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268412</t>
+          <t>259026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289760</t>
+          <t>279550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21630</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14475</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30411</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>25203</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18466</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33027</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>24810</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33218</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>48862</t>
+          <t>46440</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39857</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61205</t>
+          <t>56670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>605456</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>588897</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>619965</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>85,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>803</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>575134</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>560137</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>589932</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>87,79%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>85,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>657092</t>
+          <t>541089</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>638033</t>
+          <t>525394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>672062</t>
+          <t>555046</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1232226</t>
+          <t>1146545</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1210300</t>
+          <t>1124878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1257116</t>
+          <t>1167151</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>83118</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>68609</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>99677</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>79965</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>65167</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>94962</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>79587</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74697</t>
+          <t>65630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108726</t>
+          <t>95282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>169632</t>
+          <t>162705</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144742</t>
+          <t>142099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191558</t>
+          <t>184372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>688574</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>688574</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>688574</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>921</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>655099</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>655099</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>655099</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>746759</t>
+          <t>620676</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>746759</t>
+          <t>620676</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>746759</t>
+          <t>620676</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1401858</t>
+          <t>1309250</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1401858</t>
+          <t>1309250</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1401858</t>
+          <t>1309250</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
